--- a/task-reviews/tile/task_tile_pattern_match3_run_count/task_tile_pattern_match3_run_count.xlsx
+++ b/task-reviews/tile/task_tile_pattern_match3_run_count/task_tile_pattern_match3_run_count.xlsx
@@ -3071,12 +3071,12 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0001.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0001.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0001.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0001.json</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0023.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0023.png</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0023.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0023.json</t>
         </is>
       </c>
     </row>
@@ -3199,12 +3199,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0022.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0022.png</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0022.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0022.json</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0010.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0010.png</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0010.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0010.json</t>
         </is>
       </c>
     </row>
@@ -3327,12 +3327,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0008.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0008.png</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0008.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0008.json</t>
         </is>
       </c>
     </row>
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0013.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0013.png</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0013.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0013.json</t>
         </is>
       </c>
     </row>
@@ -3455,12 +3455,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0015.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0015.png</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0015.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0015.json</t>
         </is>
       </c>
     </row>
@@ -3519,12 +3519,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0012.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0012.png</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0012.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0012.json</t>
         </is>
       </c>
     </row>
@@ -3583,12 +3583,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0011.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0011.png</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0011.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0011.json</t>
         </is>
       </c>
     </row>
@@ -3647,12 +3647,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0004.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0004.png</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0004.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0004.json</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0005.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0005.png</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0005.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0005.json</t>
         </is>
       </c>
     </row>
@@ -3775,12 +3775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0020.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0020.png</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0020.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0020.json</t>
         </is>
       </c>
     </row>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0007.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0007.png</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0007.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0007.json</t>
         </is>
       </c>
     </row>
@@ -3903,12 +3903,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0014.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0014.png</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0014.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0014.json</t>
         </is>
       </c>
     </row>
@@ -3967,12 +3967,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0019.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0019.png</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0019.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0019.json</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0003.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0003.png</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0003.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0003.json</t>
         </is>
       </c>
     </row>
@@ -4095,12 +4095,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0006.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0006.png</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0006.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0006.json</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0021.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0021.png</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0021.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0021.json</t>
         </is>
       </c>
     </row>
@@ -4223,12 +4223,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0009.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0009.png</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0009.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0009.json</t>
         </is>
       </c>
     </row>
@@ -4287,12 +4287,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0024.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0024.png</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0024.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0024.json</t>
         </is>
       </c>
     </row>
@@ -4351,12 +4351,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0000.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0000.png</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0000.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0000.json</t>
         </is>
       </c>
     </row>
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0002.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0002.png</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0002.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0002.json</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0016.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0016.png</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0016.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0016.json</t>
         </is>
       </c>
     </row>
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0018.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0018.png</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0018.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0018.json</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/cols/0017.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/cols/0017.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/cols/0017.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/cols/0017.json</t>
         </is>
       </c>
     </row>
@@ -4768,12 +4768,12 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0002.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0002.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0002.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0002.json</t>
         </is>
       </c>
     </row>
@@ -4832,12 +4832,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0017.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0017.png</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0017.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0017.json</t>
         </is>
       </c>
     </row>
@@ -4896,12 +4896,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0016.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0016.png</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0016.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0016.json</t>
         </is>
       </c>
     </row>
@@ -4960,12 +4960,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0014.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0014.png</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0014.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0014.json</t>
         </is>
       </c>
     </row>
@@ -5024,12 +5024,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0008.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0008.png</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0008.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0008.json</t>
         </is>
       </c>
     </row>
@@ -5088,12 +5088,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0003.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0003.png</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0003.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0003.json</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0018.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0018.png</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0018.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0018.json</t>
         </is>
       </c>
     </row>
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0024.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0024.png</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0024.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0024.json</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0006.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0006.png</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0006.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0006.json</t>
         </is>
       </c>
     </row>
@@ -5344,12 +5344,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0015.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0015.png</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0015.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0015.json</t>
         </is>
       </c>
     </row>
@@ -5408,12 +5408,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0009.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0009.png</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0009.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0009.json</t>
         </is>
       </c>
     </row>
@@ -5472,12 +5472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0011.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0011.png</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0011.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0011.json</t>
         </is>
       </c>
     </row>
@@ -5536,12 +5536,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0021.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0021.png</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0021.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0021.json</t>
         </is>
       </c>
     </row>
@@ -5600,12 +5600,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0013.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0013.png</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0013.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0013.json</t>
         </is>
       </c>
     </row>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0004.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0004.png</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0004.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0004.json</t>
         </is>
       </c>
     </row>
@@ -5728,12 +5728,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0005.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0005.png</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0005.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0005.json</t>
         </is>
       </c>
     </row>
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0019.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0019.png</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0019.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0019.json</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0022.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0022.png</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0022.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0022.json</t>
         </is>
       </c>
     </row>
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0007.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0007.png</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0007.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0007.json</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0012.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0012.png</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0012.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0012.json</t>
         </is>
       </c>
     </row>
@@ -6048,12 +6048,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0010.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0010.png</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0010.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0010.json</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0020.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0020.png</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0020.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0020.json</t>
         </is>
       </c>
     </row>
@@ -6176,12 +6176,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0001.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0001.png</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0001.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0001.json</t>
         </is>
       </c>
     </row>
@@ -6240,12 +6240,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0000.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0000.png</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0000.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0000.json</t>
         </is>
       </c>
     </row>
@@ -6304,12 +6304,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/images/rows/0023.png</t>
+          <t>tile/task_tile_pattern_match3_run_count/images/rows/0023.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>task_tile_pattern_match3_run_count/data/rows/0023.json</t>
+          <t>tile/task_tile_pattern_match3_run_count/data/rows/0023.json</t>
         </is>
       </c>
     </row>
